--- a/Unity/Assets/Config/Excel/Skill/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Skill/SkillConfig.xlsx
@@ -5,13 +5,13 @@
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="SkillData_1" sheetId="1" r:id="rId4"/>
+    <sheet name="sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
   <si>
     <t>技能ID</t>
   </si>
@@ -22,25 +22,10 @@
     <t>技能描述</t>
   </si>
   <si>
-    <t>冷却</t>
-  </si>
-  <si>
-    <t>蓝耗</t>
-  </si>
-  <si>
-    <t>前摇时间</t>
-  </si>
-  <si>
-    <t>后摇时间</t>
-  </si>
-  <si>
-    <t>总时间</t>
-  </si>
-  <si>
-    <t>释放时自身增加的buff</t>
-  </si>
-  <si>
-    <t>命中时增加的buff</t>
+    <t>技能最高等级</t>
+  </si>
+  <si>
+    <t>技能等级配置</t>
   </si>
   <si>
     <t>Id</t>
@@ -52,26 +37,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>CoolDown</t>
-  </si>
-  <si>
-    <t>ManaCost</t>
-  </si>
-  <si>
-    <t>WindupTime</t>
-  </si>
-  <si>
-    <t>RecoveryTime</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>CastBuffs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HitBuffs
-</t>
+    <t>MaxLevel</t>
+  </si>
+  <si>
+    <t>LevelConfigIds</t>
   </si>
   <si>
     <t>int</t>
@@ -80,9 +49,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>double</t>
-  </si>
-  <si>
     <t>int[]</t>
   </si>
   <si>
@@ -95,19 +61,10 @@
     <t>带有强力攻击技能</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>1.6</t>
-  </si>
-  <si>
-    <t>100</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
   </si>
   <si>
     <t>1002</t>
@@ -119,10 +76,7 @@
     <t>带有强力攻击技能2</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>278</t>
+    <t>4,5,6</t>
   </si>
   <si>
     <t>1003</t>
@@ -134,10 +88,7 @@
     <t>带有强力攻击技能3</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>222</t>
+    <t>7,8,9</t>
   </si>
 </sst>
 </file>
@@ -175,15 +126,15 @@
       <name val="微软雅黑"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="SimSong Bold"/>
+    </font>
+    <font>
       <b val="1"/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Courier"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="SimSong Bold"/>
     </font>
     <font>
       <sz val="10"/>
@@ -211,7 +162,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -284,17 +235,6 @@
         <color indexed="10"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="10"/>
       </bottom>
@@ -306,7 +246,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -325,34 +265,22 @@
     <xf numFmtId="49" fontId="4" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1439,19 +1367,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="6" defaultRowHeight="14.25" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="14.1719" style="1" customWidth="1"/>
     <col min="2" max="3" width="8.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.1719" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.3516" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1719" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.35156" style="1" customWidth="1"/>
-    <col min="8" max="10" width="10.3516" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.3516" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="6" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7422" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3984" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="6" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
@@ -1462,11 +1387,6 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2"/>
@@ -1476,11 +1396,6 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
     </row>
     <row r="3" ht="14" customHeight="1">
       <c r="A3" s="2"/>
@@ -1497,185 +1412,103 @@
       <c r="F3" t="s" s="5">
         <v>3</v>
       </c>
-      <c r="G3" t="s" s="5">
+      <c r="G3" t="s" s="6">
         <v>4</v>
-      </c>
-      <c r="H3" t="s" s="6">
-        <v>5</v>
-      </c>
-      <c r="I3" t="s" s="7">
-        <v>6</v>
-      </c>
-      <c r="J3" t="s" s="7">
-        <v>7</v>
-      </c>
-      <c r="K3" t="s" s="7">
-        <v>8</v>
-      </c>
-      <c r="L3" t="s" s="7">
-        <v>9</v>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
       <c r="C4" t="s" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s" s="5">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s" s="10">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="E4" t="s" s="9">
+        <v>7</v>
       </c>
       <c r="F4" t="s" s="5">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s" s="5">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s" s="6">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s" s="7">
-        <v>16</v>
-      </c>
-      <c r="J4" t="s" s="7">
-        <v>17</v>
-      </c>
-      <c r="K4" t="s" s="7">
-        <v>18</v>
-      </c>
-      <c r="L4" t="s" s="11">
-        <v>19</v>
+        <v>8</v>
+      </c>
+      <c r="G4" t="s" s="6">
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="4"/>
       <c r="C5" t="s" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s" s="5">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s" s="5">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s" s="5">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s" s="5">
-        <v>20</v>
-      </c>
-      <c r="H5" t="s" s="12">
-        <v>22</v>
-      </c>
-      <c r="I5" t="s" s="13">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s" s="13">
-        <v>22</v>
-      </c>
-      <c r="K5" t="s" s="13">
-        <v>23</v>
-      </c>
-      <c r="L5" t="s" s="13">
-        <v>23</v>
+        <v>10</v>
+      </c>
+      <c r="G5" t="s" s="6">
+        <v>12</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
-      <c r="C6" t="s" s="14">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s" s="14">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s" s="15">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s" s="14">
-        <v>27</v>
-      </c>
-      <c r="G6" t="s" s="14">
-        <v>28</v>
-      </c>
-      <c r="H6" t="s" s="14">
-        <v>29</v>
-      </c>
-      <c r="I6" t="s" s="14">
-        <v>29</v>
-      </c>
-      <c r="J6" t="s" s="14">
-        <v>30</v>
-      </c>
-      <c r="K6" t="s" s="14">
-        <v>31</v>
-      </c>
-      <c r="L6" s="14"/>
+      <c r="C6" t="s" s="10">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s" s="10">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s" s="11">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s" s="10">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s" s="10">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s" s="16">
-        <v>34</v>
+        <v>19</v>
+      </c>
+      <c r="E7" t="s" s="12">
+        <v>20</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+        <v>21</v>
+      </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s" s="16">
-        <v>39</v>
+        <v>23</v>
+      </c>
+      <c r="E8" t="s" s="12">
+        <v>24</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" t="s" s="2">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
